--- a/docs/仕様書/民宿管理システム.xlsx
+++ b/docs/仕様書/民宿管理システム.xlsx
@@ -2,20 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表紙" sheetId="1" r:id="R9cd7b69ccb6f4e99"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="変更履歴" sheetId="2" r:id="Re74d94373cfb43c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="概要" sheetId="3" r:id="R3eaf500c5a65411e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業務要件" sheetId="4" r:id="Ra831eb4fc98c4bfc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="機能一覧" sheetId="5" r:id="R6aedfd71e5eb4abd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="コード行別処理仕様" sheetId="6" r:id="R507e02ee0b114440"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="画面一覧" sheetId="7" r:id="Ra104d3174bab4076"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DB設計" sheetId="8" r:id="R4bbbaa26f9dc4454"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API一覧" sheetId="9" r:id="Rc0e5e19070b14562"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非機能要件" sheetId="10" r:id="R0a6c50e9b8d547bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="テスト仕様" sheetId="11" r:id="R41a3aac06fba4453"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スケジュール" sheetId="12" r:id="R496578be69704415"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参考資料" sheetId="13" r:id="Re4683b0b383f46bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="運用・基盤仕様" sheetId="14" r:id="R6a1788ca72424301"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表紙" sheetId="1" r:id="R7b225ec44a0f4fb8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="変更履歴" sheetId="2" r:id="R42d10e4788c24613"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="概要" sheetId="3" r:id="R744e4b4813664c0d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業務要件" sheetId="4" r:id="R1dc6210e5c2c482d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="機能一覧" sheetId="5" r:id="Rd2d1ad6afb2a47ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="コード行別処理仕様" sheetId="6" r:id="Rf864c2e9212240fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="画面一覧" sheetId="7" r:id="R9ccce087721b4202"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DB設計" sheetId="8" r:id="R07cf62bf5e594390"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API一覧" sheetId="9" r:id="R0cf49fd4a759426a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非機能要件" sheetId="10" r:id="Ref6a70ff613f4abd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="テスト仕様" sheetId="11" r:id="R41fa0e7b42db43d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スケジュール" sheetId="12" r:id="R97cda7e3cce3402e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参考資料" sheetId="13" r:id="R297e11a80baa4971"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="運用・基盤仕様" sheetId="14" r:id="R9db09c5e379f4a58"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -176,7 +176,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="40">
+  <x:cellXfs count="42">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -294,6 +294,12 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="2">
@@ -558,7 +564,7 @@
         <x:v>何念童</x:v>
       </x:c>
       <x:c r="C3" s="27" t="str">
-        <x:v>2026-07-13</x:v>
+        <x:v>2026-09-30</x:v>
       </x:c>
       <x:c r="D3" s="27" t="str">
         <x:v>何念童</x:v>
@@ -570,7 +576,7 @@
         <x:v>備考</x:v>
       </x:c>
       <x:c r="B4" s="27" t="str">
-        <x:v>現行 Spring Boot + React + MyBatis 実装を基準に更新</x:v>
+        <x:v>現行 Spring Boot + React + MyBatis 実装と管理端房態カレンダー v1.11 を基準に更新</x:v>
       </x:c>
       <x:c r="C4" s="26" t="str">
         <x:v>対象シート</x:v>
@@ -668,7 +674,7 @@
         <x:v>版数</x:v>
       </x:c>
       <x:c r="B12" s="30" t="str">
-        <x:v>1.9</x:v>
+        <x:v>1.11</x:v>
       </x:c>
       <x:c r="C12" s="30"/>
       <x:c r="D12" s="29" t="str">
@@ -683,7 +689,7 @@
         <x:v>更新日</x:v>
       </x:c>
       <x:c r="B13" s="30" t="str">
-        <x:v>2026-07-13</x:v>
+        <x:v>2026-09-30</x:v>
       </x:c>
       <x:c r="C13" s="30"/>
       <x:c r="D13" s="29" t="str">
@@ -965,7 +971,7 @@
         <x:v>何念童</x:v>
       </x:c>
       <x:c r="C3" s="27" t="str">
-        <x:v>2026-07-13</x:v>
+        <x:v>2026-09-30</x:v>
       </x:c>
       <x:c r="D3" s="27" t="str">
         <x:v>何念童</x:v>
@@ -1322,6 +1328,57 @@
       </x:c>
       <x:c r="E25" s="19" t="str">
         <x:v>公開URLと拒否URLが明示されていること。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="36" customHeight="1">
+      <x:c r="A26" s="40" t="str">
+        <x:v>CAL-NF-001</x:v>
+      </x:c>
+      <x:c r="B26" s="40" t="str">
+        <x:v>整合性</x:v>
+      </x:c>
+      <x:c r="C26" s="40" t="str">
+        <x:v>二重予約・二重ブロック防止</x:v>
+      </x:c>
+      <x:c r="D26" s="40" t="str">
+        <x:v>ServiceロックとPostgreSQL排他制約／triggerで競合を拒否する。</x:v>
+      </x:c>
+      <x:c r="E26" s="40" t="str">
+        <x:v>高</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="36" customHeight="1">
+      <x:c r="A27" s="40" t="str">
+        <x:v>CAL-NF-002</x:v>
+      </x:c>
+      <x:c r="B27" s="40" t="str">
+        <x:v>更新</x:v>
+      </x:c>
+      <x:c r="C27" s="40" t="str">
+        <x:v>最新状態反映</x:v>
+      </x:c>
+      <x:c r="D27" s="40" t="str">
+        <x:v>表示中のみ30秒間隔で再取得し、復帰時にも更新する。</x:v>
+      </x:c>
+      <x:c r="E27" s="40" t="str">
+        <x:v>高</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="36" customHeight="1">
+      <x:c r="A28" s="40" t="str">
+        <x:v>CAL-NF-003</x:v>
+      </x:c>
+      <x:c r="B28" s="40" t="str">
+        <x:v>監査</x:v>
+      </x:c>
+      <x:c r="C28" s="40" t="str">
+        <x:v>在庫変更履歴</x:v>
+      </x:c>
+      <x:c r="D28" s="40" t="str">
+        <x:v>ブロック変更はbefore/after、操作者、時刻を追記保存する。</x:v>
+      </x:c>
+      <x:c r="E28" s="40" t="str">
+        <x:v>高</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1395,7 +1452,7 @@
         <x:v>何念童</x:v>
       </x:c>
       <x:c r="C3" s="27" t="str">
-        <x:v>2026-07-13</x:v>
+        <x:v>2026-09-30</x:v>
       </x:c>
       <x:c r="D3" s="27" t="str">
         <x:v>何念童</x:v>
@@ -1707,7 +1764,7 @@
         <x:v>全 JUnit5 テスト / TestResultLogger</x:v>
       </x:c>
       <x:c r="F14" s="30" t="str">
-        <x:v>106件のテストが同じ証跡形式で実行され、全件成功する。</x:v>
+        <x:v>123件のテストが同じ証跡形式で実行され、全件成功する。</x:v>
       </x:c>
       <x:c r="G14" s="30" t="str">
         <x:v>中</x:v>
@@ -1720,7 +1777,7 @@
       </x:c>
       <x:c r="J14" s="30"/>
       <x:c r="K14" s="30" t="str">
-        <x:v>2026-07-13 mvn test: 106件成功</x:v>
+        <x:v>2026-09-02 mvn verify: 123件成功</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="15" hidden="0" customHeight="1">
@@ -2943,13 +3000,13 @@
         <x:v>@LoggedTest と TestResultLogger が全テストクラスに適用されている。</x:v>
       </x:c>
       <x:c r="F50" s="30" t="str">
-        <x:v>mvn test を実行</x:v>
+        <x:v>123件すべてで test_XX、注解、文字列結果を出力し成功する。</x:v>
       </x:c>
       <x:c r="G50" s="30" t="str">
         <x:v>106件すべてで test_XX、注解、文字列結果を出力し成功する。</x:v>
       </x:c>
       <x:c r="H50" s="30" t="str">
-        <x:v>Surefire: Tests run 106 / Failures 0 / Errors 0 / Skipped 0</x:v>
+        <x:v>Surefire: Tests run 123 / Failures 0 / Errors 0 / Skipped 0</x:v>
       </x:c>
       <x:c r="I50" s="30" t="str">
         <x:v>TREQ-008</x:v>
@@ -3236,6 +3293,227 @@
         <x:v>CI改善候補</x:v>
       </x:c>
       <x:c r="K58" s="19"/>
+    </x:row>
+    <x:row r="59" ht="15" hidden="0" customHeight="1">
+      <x:c r="A59" t="str">
+        <x:v>UT-043</x:v>
+      </x:c>
+      <x:c r="B59" t="str">
+        <x:v>ReservationService.findAvailableRooms</x:v>
+      </x:c>
+      <x:c r="C59" t="str">
+        <x:v>日程・人数に合う客室だけを提示したい。</x:v>
+      </x:c>
+      <x:c r="D59" t="str">
+        <x:v>期間重複、定員、当日房態をまとめて判定すること。</x:v>
+      </x:c>
+      <x:c r="E59" t="str">
+        <x:v>複数客室と既存予約あり</x:v>
+      </x:c>
+      <x:c r="F59" t="str">
+        <x:v>日程・人数を指定</x:v>
+      </x:c>
+      <x:c r="G59" t="str">
+        <x:v>条件一致する客室だけ返る。</x:v>
+      </x:c>
+      <x:c r="H59" t="str">
+        <x:v>取得客室IDが一致する。</x:v>
+      </x:c>
+      <x:c r="I59" t="str">
+        <x:v>API-010A / RULE-005</x:v>
+      </x:c>
+      <x:c r="J59" t="str">
+        <x:v>実施済</x:v>
+      </x:c>
+      <x:c r="K59" t="str">
+        <x:v>ReservationServiceLocalDbTest test_19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="15" hidden="0" customHeight="1">
+      <x:c r="A60" t="str">
+        <x:v>UT-044</x:v>
+      </x:c>
+      <x:c r="B60" t="str">
+        <x:v>ReservationService.syncTodayArrivals</x:v>
+      </x:c>
+      <x:c r="C60" t="str">
+        <x:v>当日到着を房態へ反映したい。</x:v>
+      </x:c>
+      <x:c r="D60" t="str">
+        <x:v>当日開始の booked 予約が reserved になること。</x:v>
+      </x:c>
+      <x:c r="E60" t="str">
+        <x:v>当日到着予約あり</x:v>
+      </x:c>
+      <x:c r="F60" t="str">
+        <x:v>syncTodayArrivals を実行</x:v>
+      </x:c>
+      <x:c r="G60" t="str">
+        <x:v>客室が reserved、清掃状態は維持。</x:v>
+      </x:c>
+      <x:c r="H60" t="str">
+        <x:v>DB状態が一致する。</x:v>
+      </x:c>
+      <x:c r="I60" t="str">
+        <x:v>BR-012 / LOGIC-009</x:v>
+      </x:c>
+      <x:c r="J60" t="str">
+        <x:v>実施済</x:v>
+      </x:c>
+      <x:c r="K60" t="str">
+        <x:v>ReservationServiceLocalDbTest test_20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="15" hidden="0" customHeight="1">
+      <x:c r="A61" t="str">
+        <x:v>UT-045</x:v>
+      </x:c>
+      <x:c r="B61" t="str">
+        <x:v>退室・清掃同期</x:v>
+      </x:c>
+      <x:c r="C61" t="str">
+        <x:v>同日後続予約の房態を保護したい。</x:v>
+      </x:c>
+      <x:c r="D61" t="str">
+        <x:v>退室・清掃更新後も後続予約があれば reserved を維持すること。</x:v>
+      </x:c>
+      <x:c r="E61" t="str">
+        <x:v>退室対象と同日後続予約あり</x:v>
+      </x:c>
+      <x:c r="F61" t="str">
+        <x:v>同期後に清掃済みへ更新</x:v>
+      </x:c>
+      <x:c r="G61" t="str">
+        <x:v>reserved を維持し清掃状態だけ更新。</x:v>
+      </x:c>
+      <x:c r="H61" t="str">
+        <x:v>DB状態が一致する。</x:v>
+      </x:c>
+      <x:c r="I61" t="str">
+        <x:v>REQ-009 / LOGIC-011</x:v>
+      </x:c>
+      <x:c r="J61" t="str">
+        <x:v>実施済</x:v>
+      </x:c>
+      <x:c r="K61" t="str">
+        <x:v>ReservationServiceLocalDbTest test_18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="36" customHeight="1">
+      <x:c r="A62" s="40" t="str">
+        <x:v>UT-CAL-001</x:v>
+      </x:c>
+      <x:c r="B62" s="40" t="str">
+        <x:v>RoomCalendarController</x:v>
+      </x:c>
+      <x:c r="C62" s="40" t="str">
+        <x:v>認証・CSRF</x:v>
+      </x:c>
+      <x:c r="D62" s="40" t="str">
+        <x:v>管理者認証あり</x:v>
+      </x:c>
+      <x:c r="E62" s="40" t="str">
+        <x:v>GETとPOSTを実行</x:v>
+      </x:c>
+      <x:c r="F62" s="40" t="str">
+        <x:v>未認証401、CSRFなし403、正常200/201</x:v>
+      </x:c>
+      <x:c r="G62" s="40" t="str">
+        <x:v>実施済</x:v>
+      </x:c>
+      <x:c r="H62" s="40" t="str">
+        <x:v>RoomCalendarControllerTest</x:v>
+      </x:c>
+      <x:c r="I62" s="40"/>
+      <x:c r="J62" s="40"/>
+      <x:c r="K62" s="40"/>
+    </x:row>
+    <x:row r="63" ht="36" customHeight="1">
+      <x:c r="A63" s="40" t="str">
+        <x:v>UT-CAL-002</x:v>
+      </x:c>
+      <x:c r="B63" s="40" t="str">
+        <x:v>RoomCalendarService</x:v>
+      </x:c>
+      <x:c r="C63" s="40" t="str">
+        <x:v>半開区間・競合</x:v>
+      </x:c>
+      <x:c r="D63" s="40" t="str">
+        <x:v>予約とブロックあり</x:v>
+      </x:c>
+      <x:c r="E63" s="40" t="str">
+        <x:v>境界日と重複期間を登録</x:v>
+      </x:c>
+      <x:c r="F63" s="40" t="str">
+        <x:v>同日入替可、重複409相当</x:v>
+      </x:c>
+      <x:c r="G63" s="40" t="str">
+        <x:v>実施済</x:v>
+      </x:c>
+      <x:c r="H63" s="40" t="str">
+        <x:v>RoomCalendarServiceLocalDbTest</x:v>
+      </x:c>
+      <x:c r="I63" s="40"/>
+      <x:c r="J63" s="40"/>
+      <x:c r="K63" s="40"/>
+    </x:row>
+    <x:row r="64" ht="36" customHeight="1">
+      <x:c r="A64" s="40" t="str">
+        <x:v>UT-CAL-003</x:v>
+      </x:c>
+      <x:c r="B64" s="40" t="str">
+        <x:v>在庫解除</x:v>
+      </x:c>
+      <x:c r="C64" s="40" t="str">
+        <x:v>全部・先頭・末尾・中間</x:v>
+      </x:c>
+      <x:c r="D64" s="40" t="str">
+        <x:v>有効ブロックあり</x:v>
+      </x:c>
+      <x:c r="E64" s="40" t="str">
+        <x:v>解除範囲を変更</x:v>
+      </x:c>
+      <x:c r="F64" s="40" t="str">
+        <x:v>取消または左右へ分割し監査記録</x:v>
+      </x:c>
+      <x:c r="G64" s="40" t="str">
+        <x:v>実施済</x:v>
+      </x:c>
+      <x:c r="H64" s="40" t="str">
+        <x:v>RoomCalendarServiceLocalDbTest</x:v>
+      </x:c>
+      <x:c r="I64" s="40"/>
+      <x:c r="J64" s="40"/>
+      <x:c r="K64" s="40"/>
+    </x:row>
+    <x:row r="65" ht="36" customHeight="1">
+      <x:c r="A65" s="40" t="str">
+        <x:v>UT-CAL-004</x:v>
+      </x:c>
+      <x:c r="B65" s="40" t="str">
+        <x:v>PostgreSQL</x:v>
+      </x:c>
+      <x:c r="C65" s="40" t="str">
+        <x:v>GiST・trigger</x:v>
+      </x:c>
+      <x:c r="D65" s="40" t="str">
+        <x:v>実PostgreSQL</x:v>
+      </x:c>
+      <x:c r="E65" s="40" t="str">
+        <x:v>Flyway V5と競合書込を実行</x:v>
+      </x:c>
+      <x:c r="F65" s="40" t="str">
+        <x:v>DB制約で競合拒否</x:v>
+      </x:c>
+      <x:c r="G65" s="40" t="str">
+        <x:v>配備前確認</x:v>
+      </x:c>
+      <x:c r="H65" s="40" t="str">
+        <x:v>H2では検証不可</x:v>
+      </x:c>
+      <x:c r="I65" s="40"/>
+      <x:c r="J65" s="40"/>
+      <x:c r="K65" s="40"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -3297,7 +3575,7 @@
         <x:v>何念童</x:v>
       </x:c>
       <x:c r="C3" s="27" t="str">
-        <x:v>2026-07-13</x:v>
+        <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="D3" s="27" t="str">
         <x:v>何念童</x:v>
@@ -3464,7 +3742,7 @@
         <x:v>何念童</x:v>
       </x:c>
       <x:c r="F11" s="30" t="str">
-        <x:v>JUnit5 106件、WebMvc、H2 DB連携、Scheduler、フロント build/lint、v1.9仕様書</x:v>
+        <x:v>JUnit5 123件、WebMvc、H2 DB連携、Scheduler、フロント build/lint、v1.10仕様書</x:v>
       </x:c>
       <x:c r="G11" s="30" t="str">
         <x:v>mvn test / npm lint / npm build / 全シート視覚確認</x:v>
@@ -3520,7 +3798,7 @@
         <x:v>何念童</x:v>
       </x:c>
       <x:c r="C3" s="27" t="str">
-        <x:v>2026-07-13</x:v>
+        <x:v>2026-09-30</x:v>
       </x:c>
       <x:c r="D3" s="27" t="str">
         <x:v>何念童</x:v>
@@ -3824,6 +4102,62 @@
       </x:c>
       <x:c r="D25" s="19" t="str">
         <x:v>src/test/java/com/example/minshuku/service/CheckoutSchedulerTest.java</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="36" customHeight="1">
+      <x:c r="A26" s="40" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B26" s="40" t="str">
+        <x:v>白馬樹海_管理端房態カレンダー仕様書.md</x:v>
+      </x:c>
+      <x:c r="C26" s="40" t="str">
+        <x:v>房態カレンダーの画面、API、DB、ロック、監査、受入条件。</x:v>
+      </x:c>
+      <x:c r="D26" s="40" t="str">
+        <x:v>docs/仕様書/白馬樹海_管理端房態カレンダー仕様書.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="36" customHeight="1">
+      <x:c r="A27" s="40" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B27" s="40" t="str">
+        <x:v>RoomCalendarService.java</x:v>
+      </x:c>
+      <x:c r="C27" s="40" t="str">
+        <x:v>月間投影と在庫・予約操作の業務ロジック。</x:v>
+      </x:c>
+      <x:c r="D27" s="40" t="str">
+        <x:v>src/main/java/com/example/minshuku/service/RoomCalendarService.java</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="36" customHeight="1">
+      <x:c r="A28" s="40" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B28" s="40" t="str">
+        <x:v>V5__room_inventory_calendar.sql</x:v>
+      </x:c>
+      <x:c r="C28" s="40" t="str">
+        <x:v>在庫ブロック、監査、排他制約、競合trigger。</x:v>
+      </x:c>
+      <x:c r="D28" s="40" t="str">
+        <x:v>src/main/resources/db/migration/V5__room_inventory_calendar.sql</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="36" customHeight="1">
+      <x:c r="A29" s="40" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B29" s="40" t="str">
+        <x:v>RoomCalendarControllerTest.java</x:v>
+      </x:c>
+      <x:c r="C29" s="40" t="str">
+        <x:v>認証、CSRF、正常、競合のWebMvcテスト。</x:v>
+      </x:c>
+      <x:c r="D29" s="40" t="str">
+        <x:v>src/test/java/com/example/minshuku/controller/RoomCalendarControllerTest.java</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3881,7 +4215,7 @@
         <x:v>何念童</x:v>
       </x:c>
       <x:c r="C3" s="39" t="str">
-        <x:v>2026-07-13</x:v>
+        <x:v>2026-09-30</x:v>
       </x:c>
       <x:c r="D3" s="39" t="str">
         <x:v>何念童</x:v>
@@ -3948,7 +4282,7 @@
         <x:v>期限到来チェックアウト</x:v>
       </x:c>
       <x:c r="D7" s="39" t="str">
-        <x:v>GET API は参照専用とし、CheckoutScheduler が既定で毎時0分に syncDueCheckouts を実行する。</x:v>
+        <x:v>GET API は参照専用とし、CheckoutScheduler が既定で毎分、syncDueCheckouts と syncTodayArrivals を実行する。</x:v>
       </x:c>
       <x:c r="E7" s="39" t="str">
         <x:v>GET 呼出しで更新されず、scheduler 単体テストと Service DBテストが成功すること。</x:v>
@@ -4115,6 +4449,46 @@
       </x:c>
       <x:c r="F15" s="19" t="str">
         <x:v>SecurityConfig.java / 配備設定</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="36" customHeight="1">
+      <x:c r="A16" s="40" t="str">
+        <x:v>OPS-CAL-001</x:v>
+      </x:c>
+      <x:c r="B16" s="40" t="str">
+        <x:v>運用</x:v>
+      </x:c>
+      <x:c r="C16" s="40" t="str">
+        <x:v>房態カレンダー</x:v>
+      </x:c>
+      <x:c r="D16" s="40" t="str">
+        <x:v>管理者画面は30秒更新と復帰時更新を行い、更新失敗時も直前表示を保持する。</x:v>
+      </x:c>
+      <x:c r="E16" s="40" t="str">
+        <x:v>可視状態と復帰時にAPI通信を確認する。</x:v>
+      </x:c>
+      <x:c r="F16" s="40" t="str">
+        <x:v>RoomCalendar.jsx</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="36" customHeight="1">
+      <x:c r="A17" s="40" t="str">
+        <x:v>OPS-CAL-002</x:v>
+      </x:c>
+      <x:c r="B17" s="40" t="str">
+        <x:v>DB</x:v>
+      </x:c>
+      <x:c r="C17" s="40" t="str">
+        <x:v>PostgreSQL V5</x:v>
+      </x:c>
+      <x:c r="D17" s="40" t="str">
+        <x:v>本番前にFlyway V5、GiST排他制約、相互競合triggerを実PostgreSQLで確認する。</x:v>
+      </x:c>
+      <x:c r="E17" s="40" t="str">
+        <x:v>mvn verifyに加え実DB統合試験を実施する。</x:v>
+      </x:c>
+      <x:c r="F17" s="40" t="str">
+        <x:v>V5__room_inventory_calendar.sql</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4169,7 +4543,7 @@
         <x:v>何念童</x:v>
       </x:c>
       <x:c r="C3" s="27" t="str">
-        <x:v>2026-07-13</x:v>
+        <x:v>2026-09-30</x:v>
       </x:c>
       <x:c r="D3" s="27" t="str">
         <x:v>何念童</x:v>
@@ -4364,6 +4738,36 @@
         <x:v>何念童</x:v>
       </x:c>
       <x:c r="E16" s="19"/>
+    </x:row>
+    <x:row r="17" ht="15" hidden="0" customHeight="1">
+      <x:c r="A17" t="str">
+        <x:v>1.10</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>2026-09-02</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>宿泊数自動計算、日程・人数別の空室候補、到着日房態同期、同日後続予約を保護する清掃・退室同期を実装とテストへ反映</x:v>
+      </x:c>
+      <x:c r="D17" t="str">
+        <x:v>何念童</x:v>
+      </x:c>
+      <x:c r="E17"/>
+    </x:row>
+    <x:row r="18" ht="36" customHeight="1">
+      <x:c r="A18" s="40" t="str">
+        <x:v>1.11</x:v>
+      </x:c>
+      <x:c r="B18" s="40" t="str">
+        <x:v>2026-09-30</x:v>
+      </x:c>
+      <x:c r="C18" s="40" t="str">
+        <x:v>管理端房態カレンダー、在庫ブロック、半開区間、競合制御、監査、30秒更新、関連テストを反映</x:v>
+      </x:c>
+      <x:c r="D18" s="40" t="str">
+        <x:v>何念童</x:v>
+      </x:c>
+      <x:c r="E18" s="40"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -4414,7 +4818,7 @@
         <x:v>何念童</x:v>
       </x:c>
       <x:c r="C3" s="27" t="str">
-        <x:v>2026-07-13</x:v>
+        <x:v>2026-09-30</x:v>
       </x:c>
       <x:c r="D3" s="27" t="str">
         <x:v>何念童</x:v>
@@ -4521,7 +4925,7 @@
         <x:v>民宿運用では、予約、客室状態、清掃状態、期間別料金を一元管理する必要がある。</x:v>
       </x:c>
       <x:c r="D11" s="30" t="str">
-        <x:v>業務上の必要性を確認する。</x:v>
+        <x:v>予約日程・人数と実房態の整合性を確認する。</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
@@ -4723,7 +5127,7 @@
         <x:v>チェックアウト同期</x:v>
       </x:c>
       <x:c r="D26" s="19" t="str">
-        <x:v>@EnableScheduling と CheckoutScheduler により毎時0分（Asia/Tokyo）に期限到来予約を同期し、GET API は更新を行わない。</x:v>
+        <x:v>@EnableScheduling と CheckoutScheduler により毎分（Asia/Tokyo）に期限到来チェックアウトと当日到着予約を同期し、GET API は更新を行わない。</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -4738,6 +5142,34 @@
       </x:c>
       <x:c r="D27" s="19" t="str">
         <x:v>予約中・取消済み・チェックアウト済みを独立した5件ページで返し、各 PageResponse に totalCount を含める。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="36" customHeight="1">
+      <x:c r="A28" s="40" t="str">
+        <x:v>BASE-013</x:v>
+      </x:c>
+      <x:c r="B28" s="40" t="str">
+        <x:v>在庫管理</x:v>
+      </x:c>
+      <x:c r="C28" s="40" t="str">
+        <x:v>管理端房態カレンダー</x:v>
+      </x:c>
+      <x:c r="D28" s="40" t="str">
+        <x:v>自然月 Tape Chart で予約、販売停止、メンテナンスを客室別に一元表示する。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="36" customHeight="1">
+      <x:c r="A29" s="40" t="str">
+        <x:v>BASE-014</x:v>
+      </x:c>
+      <x:c r="B29" s="40" t="str">
+        <x:v>期間規則</x:v>
+      </x:c>
+      <x:c r="C29" s="40" t="str">
+        <x:v>半開区間</x:v>
+      </x:c>
+      <x:c r="D29" s="40" t="str">
+        <x:v>予約・在庫ブロックは [開始日, 退房日／販売再開日) で判定し、終了日は占有しない。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4794,7 +5226,7 @@
         <x:v>何念童</x:v>
       </x:c>
       <x:c r="C3" s="27" t="str">
-        <x:v>2026-07-13</x:v>
+        <x:v>2026-09-30</x:v>
       </x:c>
       <x:c r="D3" s="27" t="str">
         <x:v>何念童</x:v>
@@ -4857,7 +5289,7 @@
         <x:v>予約登録</x:v>
       </x:c>
       <x:c r="D7" s="30" t="str">
-        <x:v>空室かつ清掃済みの客室に対して、宿泊者・日程・人数・同行者を登録できる。</x:v>
+        <x:v>日程・人数に合い、他予約と重複しない有効客室に対して、宿泊者・同行者を登録できる。</x:v>
       </x:c>
       <x:c r="E7" s="30" t="str">
         <x:v>高</x:v>
@@ -5077,7 +5509,7 @@
         <x:v>料金重複防止</x:v>
       </x:c>
       <x:c r="D18" s="30" t="str">
-        <x:v>同一客室で期間が重なる料金ルールを拒否する。</x:v>
+        <x:v>宿泊終了日を迎えた予約をチェックアウト済みにし、当日到着予約を予約済み房態へ同期する。</x:v>
       </x:c>
       <x:c r="E18" s="30" t="str">
         <x:v>高</x:v>
@@ -5377,7 +5809,7 @@
         <x:v>清掃管理</x:v>
       </x:c>
       <x:c r="D33" s="30" t="str">
-        <x:v>チェックアウト後の清掃状態を管理できること。</x:v>
+        <x:v>チェックアウト後の清掃状態を管理し、同日に他の予約がある場合はその予約の宿泊状態を維持できること。</x:v>
       </x:c>
       <x:c r="E33" s="30" t="str">
         <x:v>checked_out 予約の客室を needs_cleaning / cleaned に更新できる。</x:v>
@@ -5417,7 +5849,7 @@
         <x:v>ダッシュボード</x:v>
       </x:c>
       <x:c r="D35" s="30" t="str">
-        <x:v>現在の客室・予約状況を参照できること。</x:v>
+        <x:v>CheckoutScheduler が毎分、期限到来チェックアウトと当日到着を同期した永続化済み状態を GET API が読取専用で返す。</x:v>
       </x:c>
       <x:c r="E35" s="30" t="str">
         <x:v>CheckoutScheduler が定期同期した永続化済み状態を GET API が読取専用で返す。</x:v>
@@ -5577,7 +6009,7 @@
         <x:v>客室検証</x:v>
       </x:c>
       <x:c r="D43" s="30" t="str">
-        <x:v>active=true、occupancy_status=vacant、cleaning_status=cleaned、人数 &lt;= 定員</x:v>
+        <x:v>active=true、人数&lt;=定員、対象期間に有効予約との重複なし。当日入室は vacant / cleaned も満たす。</x:v>
       </x:c>
       <x:c r="E43" s="30" t="str">
         <x:v>予約対象として確定</x:v>
@@ -5797,13 +6229,53 @@
         <x:v>CheckoutScheduler 実行時</x:v>
       </x:c>
       <x:c r="D54" s="19" t="str">
-        <x:v>booked かつ check_out_date &lt;= DB CURRENT_DATE</x:v>
+        <x:v>booked かつ check_out_date &lt;= DB CURRENT_DATE、または booked かつ check_in_date = DB CURRENT_DATE</x:v>
       </x:c>
       <x:c r="E54" s="19" t="str">
-        <x:v>予約を checked_out、客室を vacant / needs_cleaning に同期</x:v>
+        <x:v>退室は checked_out、当日到着は reserved。清掃更新時も他予約に合わせて occupied / reserved / vacant を再計算</x:v>
       </x:c>
       <x:c r="F54" s="19" t="str">
         <x:v>GET /dashboard・/reservations は状態更新しない</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="36" customHeight="1">
+      <x:c r="A55" s="40" t="str">
+        <x:v>CAL-BR-001</x:v>
+      </x:c>
+      <x:c r="B55" s="40" t="str">
+        <x:v>房態</x:v>
+      </x:c>
+      <x:c r="C55" s="40" t="str">
+        <x:v>月間房態表示</x:v>
+      </x:c>
+      <x:c r="D55" s="40" t="str">
+        <x:v>管理者が自然月単位で全客室の予約・販売停止・メンテナンスを確認できる。</x:v>
+      </x:c>
+      <x:c r="E55" s="40" t="str">
+        <x:v>高</x:v>
+      </x:c>
+      <x:c r="F55" s="40" t="str">
+        <x:v>RoomCalendar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="36" customHeight="1">
+      <x:c r="A56" s="40" t="str">
+        <x:v>CAL-RULE-001</x:v>
+      </x:c>
+      <x:c r="B56" s="40" t="str">
+        <x:v>競合制御</x:v>
+      </x:c>
+      <x:c r="C56" s="40" t="str">
+        <x:v>在庫更新</x:v>
+      </x:c>
+      <x:c r="D56" s="40" t="str">
+        <x:v>客室行をロック後、予約と有効ブロックの重複を再検証する。</x:v>
+      </x:c>
+      <x:c r="E56" s="40" t="str">
+        <x:v>競合なしなら同一トランザクションで保存</x:v>
+      </x:c>
+      <x:c r="F56" s="40" t="str">
+        <x:v>競合時は HTTP 409</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5869,7 +6341,7 @@
         <x:v>何念童</x:v>
       </x:c>
       <x:c r="C3" s="27" t="str">
-        <x:v>2026-07-13</x:v>
+        <x:v>2026-09-30</x:v>
       </x:c>
       <x:c r="D3" s="27" t="str">
         <x:v>何念童</x:v>
@@ -6008,7 +6480,7 @@
         <x:v>予約登録</x:v>
       </x:c>
       <x:c r="D9" s="30" t="str">
-        <x:v>入力検証、客室ロック、重複確認、料金計算、同行者保存を行う。</x:v>
+        <x:v>宿泊数を日付差で算出し、日程・人数で空室候補を取得後、入力検証・客室ロック・重複確認・料金計算・同行者保存を行う。</x:v>
       </x:c>
       <x:c r="E9" s="30" t="str">
         <x:v>ReservationCreateRequest</x:v>
@@ -6153,7 +6625,7 @@
         <x:v>清掃状態更新</x:v>
       </x:c>
       <x:c r="D14" s="30" t="str">
-        <x:v>チェックアウト後の客室清掃状態を更新する。</x:v>
+        <x:v>チェックアウト後の清掃状態を更新し、同日後続予約または滞在中予約の宿泊状態を維持する。</x:v>
       </x:c>
       <x:c r="E14" s="30" t="str">
         <x:v>CleaningRequest</x:v>
@@ -6414,7 +6886,7 @@
         <x:v>定期チェックアウト同期</x:v>
       </x:c>
       <x:c r="D23" s="19" t="str">
-        <x:v>毎時0分に期限到来予約を同期し、参照APIから更新処理を分離する。</x:v>
+        <x:v>毎分、期限到来チェックアウトと当日到着予約を同期し、参照APIから更新処理を分離する。</x:v>
       </x:c>
       <x:c r="E23" s="19" t="str">
         <x:v>cron / timezone</x:v>
@@ -6733,10 +7205,10 @@
         <x:v>ApiController</x:v>
       </x:c>
       <x:c r="D34" s="30" t="str">
-        <x:v>deleteCancelledReservation</x:v>
+        <x:v>日程・人数を受け取り、期間重複・定員・当日房態を判定して予約可能客室を返す。</x:v>
       </x:c>
       <x:c r="E34" s="30" t="str">
-        <x:v>取消済み予約削除 API を受け取り、Service の deleteCancelled へ委譲する。</x:v>
+        <x:v>GET /api/reservations/available-rooms</x:v>
       </x:c>
       <x:c r="F34" s="30" t="str">
         <x:v>POST /api/reservations/{id}/delete</x:v>
@@ -6907,7 +7379,7 @@
         <x:v>ReservationService</x:v>
       </x:c>
       <x:c r="D40" s="30" t="str">
-        <x:v>syncDueCheckouts</x:v>
+        <x:v>期限到来予約を checked_out にし、同日他予約を確認して客室を occupied / reserved / vacant と needs_cleaning に同期する。</x:v>
       </x:c>
       <x:c r="E40" s="30" t="str">
         <x:v>booked かつ check_out_date &lt;= CURRENT_DATE の予約を checked_out にし、客室を vacant / needs_cleaning にする。</x:v>
@@ -6965,7 +7437,7 @@
         <x:v>ReservationService</x:v>
       </x:c>
       <x:c r="D42" s="30" t="str">
-        <x:v>updateCheckoutCleaningStatus</x:v>
+        <x:v>checked_out 予約の清掃状態を更新し、同日他予約の状態を優先して客室の宿泊状態を再計算する。</x:v>
       </x:c>
       <x:c r="E42" s="30" t="str">
         <x:v>予約を取得し、checked_out 予約だけ清掃状態許可値を検証して客室を vacant のまま更新する。</x:v>
@@ -7139,7 +7611,7 @@
         <x:v>RoomMapper.xml</x:v>
       </x:c>
       <x:c r="D48" s="30" t="str">
-        <x:v>findBookable</x:v>
+        <x:v>findAvailableForStay で active、定員、期間重複、当日 vacant / cleaned を判定して候補を取得する。</x:v>
       </x:c>
       <x:c r="E48" s="30" t="str">
         <x:v>active=true、vacant、cleaned の客室を予約フォーム候補として取得する。</x:v>
@@ -7226,7 +7698,7 @@
         <x:v>CheckoutScheduler</x:v>
       </x:c>
       <x:c r="D51" s="19" t="str">
-        <x:v>syncDueCheckouts</x:v>
+        <x:v>設定可能な cron / timezone で syncDueCheckouts と syncTodayArrivals を順に実行する。</x:v>
       </x:c>
       <x:c r="E51" s="19" t="str">
         <x:v>設定可能な cron / timezone で ReservationService.syncDueCheckouts を委譲実行する。</x:v>
@@ -7241,7 +7713,7 @@
         <x:v>Service側</x:v>
       </x:c>
       <x:c r="I51" s="19" t="str">
-        <x:v>既定: 0 0 * * * * / Asia/Tokyo</x:v>
+        <x:v>既定: 0 * * * * * / Asia/Tokyo</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="15" hidden="0" customHeight="1">
@@ -7757,6 +8229,118 @@
         <x:v>ReservationService へ委譲</x:v>
       </x:c>
       <x:c r="I71" s="19"/>
+    </x:row>
+    <x:row r="72" ht="36" customHeight="1">
+      <x:c r="A72" s="40" t="str">
+        <x:v>F-CAL-001</x:v>
+      </x:c>
+      <x:c r="B72" s="40" t="str">
+        <x:v>房態</x:v>
+      </x:c>
+      <x:c r="C72" s="40" t="str">
+        <x:v>自然月カレンダー</x:v>
+      </x:c>
+      <x:c r="D72" s="40" t="str">
+        <x:v>客室行×日付列の Tape Chart を表示し、予約と在庫ブロックを帯で示す。</x:v>
+      </x:c>
+      <x:c r="E72" s="40" t="str">
+        <x:v>month</x:v>
+      </x:c>
+      <x:c r="F72" s="40" t="str">
+        <x:v>CalendarView</x:v>
+      </x:c>
+      <x:c r="G72" s="40" t="str">
+        <x:v>管理者</x:v>
+      </x:c>
+      <x:c r="H72" s="40" t="str">
+        <x:v>高</x:v>
+      </x:c>
+      <x:c r="I72" s="40" t="str">
+        <x:v>RoomCalendarController / RoomCalendarService</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" ht="36" customHeight="1">
+      <x:c r="A73" s="40" t="str">
+        <x:v>F-CAL-002</x:v>
+      </x:c>
+      <x:c r="B73" s="40" t="str">
+        <x:v>在庫</x:v>
+      </x:c>
+      <x:c r="C73" s="40" t="str">
+        <x:v>販売停止・メンテナンス</x:v>
+      </x:c>
+      <x:c r="D73" s="40" t="str">
+        <x:v>空き期間からブロックを作成・更新・全部／一部解除する。</x:v>
+      </x:c>
+      <x:c r="E73" s="40" t="str">
+        <x:v>roomId / blockType / [start,end)</x:v>
+      </x:c>
+      <x:c r="F73" s="40" t="str">
+        <x:v>BlockView</x:v>
+      </x:c>
+      <x:c r="G73" s="40" t="str">
+        <x:v>管理者</x:v>
+      </x:c>
+      <x:c r="H73" s="40" t="str">
+        <x:v>高</x:v>
+      </x:c>
+      <x:c r="I73" s="40" t="str">
+        <x:v>RoomCalendarService</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" ht="36" customHeight="1">
+      <x:c r="A74" s="40" t="str">
+        <x:v>JAVA-CAL-001</x:v>
+      </x:c>
+      <x:c r="B74" s="40" t="str">
+        <x:v>service</x:v>
+      </x:c>
+      <x:c r="C74" s="40" t="str">
+        <x:v>RoomCalendarService</x:v>
+      </x:c>
+      <x:c r="D74" s="40" t="str">
+        <x:v>月間投影、競合判定、ロック、分割解除、監査記録、予約操作を担当する。</x:v>
+      </x:c>
+      <x:c r="E74" s="40" t="str">
+        <x:v>calendar / createBlock / releaseBlock</x:v>
+      </x:c>
+      <x:c r="F74" s="40" t="str">
+        <x:v>RoomInventoryMapper</x:v>
+      </x:c>
+      <x:c r="G74" s="40" t="str">
+        <x:v>業務ロジック</x:v>
+      </x:c>
+      <x:c r="H74" s="40" t="str">
+        <x:v>高</x:v>
+      </x:c>
+      <x:c r="I74" s="40"/>
+    </x:row>
+    <x:row r="75" ht="36" customHeight="1">
+      <x:c r="A75" s="40" t="str">
+        <x:v>JAVA-CAL-002</x:v>
+      </x:c>
+      <x:c r="B75" s="40" t="str">
+        <x:v>mapper</x:v>
+      </x:c>
+      <x:c r="C75" s="40" t="str">
+        <x:v>RoomInventoryMapper</x:v>
+      </x:c>
+      <x:c r="D75" s="40" t="str">
+        <x:v>在庫ブロックと追記型監査イベントを永続化する。</x:v>
+      </x:c>
+      <x:c r="E75" s="40" t="str">
+        <x:v>findEffective / insert / cancel / insertEvent</x:v>
+      </x:c>
+      <x:c r="F75" s="40" t="str">
+        <x:v>RoomInventoryMapper.xml</x:v>
+      </x:c>
+      <x:c r="G75" s="40" t="str">
+        <x:v>DAO</x:v>
+      </x:c>
+      <x:c r="H75" s="40" t="str">
+        <x:v>高</x:v>
+      </x:c>
+      <x:c r="I75" s="40"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -7807,7 +8391,7 @@
         <x:v>何念童</x:v>
       </x:c>
       <x:c r="C3" s="27" t="str">
-        <x:v>2026-07-13</x:v>
+        <x:v>2026-09-02</x:v>
       </x:c>
       <x:c r="D3" s="27" t="str">
         <x:v>何念童</x:v>
@@ -11368,7 +11952,7 @@
         <x:v>何念童</x:v>
       </x:c>
       <x:c r="C3" s="27" t="str">
-        <x:v>2026-07-13</x:v>
+        <x:v>2026-09-30</x:v>
       </x:c>
       <x:c r="D3" s="27" t="str">
         <x:v>何念童</x:v>
@@ -11640,6 +12224,52 @@
       </x:c>
       <x:c r="G16" s="30" t="str">
         <x:v>料金ルールは予約金額計算の根拠として使用する。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="36" customHeight="1">
+      <x:c r="A17" s="40" t="str">
+        <x:v>S-CAL-001</x:v>
+      </x:c>
+      <x:c r="B17" s="40" t="str">
+        <x:v>房態カレンダー</x:v>
+      </x:c>
+      <x:c r="C17" s="40" t="str">
+        <x:v>管理者</x:v>
+      </x:c>
+      <x:c r="D17" s="40" t="str">
+        <x:v>自然月の全客室を横軸日付の Tape Chart で確認・操作する。</x:v>
+      </x:c>
+      <x:c r="E17" s="40" t="str">
+        <x:v>月移動、予約帯、販売停止、メンテナンス、詳細モーダル</x:v>
+      </x:c>
+      <x:c r="F17" s="40" t="str">
+        <x:v>共通ナビ</x:v>
+      </x:c>
+      <x:c r="G17" s="40" t="str">
+        <x:v>同画面</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="36" customHeight="1">
+      <x:c r="A18" s="40" t="str">
+        <x:v>SCR-CAL-001</x:v>
+      </x:c>
+      <x:c r="B18" s="40" t="str">
+        <x:v>/jukai-internal/calendar</x:v>
+      </x:c>
+      <x:c r="C18" s="40" t="str">
+        <x:v>DashboardController</x:v>
+      </x:c>
+      <x:c r="D18" s="40" t="str">
+        <x:v>GET /api/room-calendar</x:v>
+      </x:c>
+      <x:c r="E18" s="40" t="str">
+        <x:v>rooms / stays / blocks / today</x:v>
+      </x:c>
+      <x:c r="F18" s="40" t="str">
+        <x:v>空き期間選択、予約・ブロック操作</x:v>
+      </x:c>
+      <x:c r="G18" s="40" t="str">
+        <x:v>30秒更新。詳細は選択時に取得。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -11699,7 +12329,7 @@
         <x:v>何念童</x:v>
       </x:c>
       <x:c r="C3" s="27" t="str">
-        <x:v>2026-07-13</x:v>
+        <x:v>2026-09-30</x:v>
       </x:c>
       <x:c r="D3" s="27" t="str">
         <x:v>何念童</x:v>
@@ -11930,24 +12560,24 @@
         <x:v>論理削除フラグ。</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="24" hidden="0" customHeight="1">
-      <x:c r="A16" s="30" t="str">
+    <x:row r="16" ht="36" hidden="0" customHeight="1">
+      <x:c r="A16" s="41" t="str">
         <x:v>reservations</x:v>
       </x:c>
-      <x:c r="B16" s="30" t="str">
+      <x:c r="B16" s="41" t="str">
         <x:v>id</x:v>
       </x:c>
-      <x:c r="C16" s="30" t="str">
+      <x:c r="C16" s="41" t="str">
         <x:v>INTEGER GENERATED BY DEFAULT AS IDENTITY</x:v>
       </x:c>
-      <x:c r="D16" s="30" t="str">
+      <x:c r="D16" s="41" t="str">
         <x:v>YES</x:v>
       </x:c>
-      <x:c r="E16" s="30"/>
-      <x:c r="F16" s="30" t="str">
+      <x:c r="E16" s="41"/>
+      <x:c r="F16" s="41" t="str">
         <x:v>NO</x:v>
       </x:c>
-      <x:c r="G16" s="30" t="str">
+      <x:c r="G16" s="41" t="str">
         <x:v>予約ID。</x:v>
       </x:c>
     </x:row>
@@ -13346,6 +13976,166 @@
       </x:c>
       <x:c r="G83" s="19" t="str">
         <x:v>本番Flywayとは別管理</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" ht="36" customHeight="1">
+      <x:c r="A84" s="40" t="str">
+        <x:v>room_inventory_blocks</x:v>
+      </x:c>
+      <x:c r="B84" s="40" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="C84" s="40" t="str">
+        <x:v>BIGINT GENERATED BY DEFAULT AS IDENTITY</x:v>
+      </x:c>
+      <x:c r="D84" s="40" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="E84" s="40"/>
+      <x:c r="F84" s="40" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="G84" s="40" t="str">
+        <x:v>在庫ブロックID。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" ht="36" customHeight="1">
+      <x:c r="A85" s="40" t="str">
+        <x:v>room_inventory_blocks</x:v>
+      </x:c>
+      <x:c r="B85" s="40" t="str">
+        <x:v>room_id</x:v>
+      </x:c>
+      <x:c r="C85" s="40" t="str">
+        <x:v>BIGINT</x:v>
+      </x:c>
+      <x:c r="D85" s="40"/>
+      <x:c r="E85" s="40" t="str">
+        <x:v>rooms.id</x:v>
+      </x:c>
+      <x:c r="F85" s="40" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="G85" s="40" t="str">
+        <x:v>対象客室。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" ht="36" customHeight="1">
+      <x:c r="A86" s="40" t="str">
+        <x:v>room_inventory_blocks</x:v>
+      </x:c>
+      <x:c r="B86" s="40" t="str">
+        <x:v>block_type</x:v>
+      </x:c>
+      <x:c r="C86" s="40" t="str">
+        <x:v>VARCHAR(20)</x:v>
+      </x:c>
+      <x:c r="D86" s="40"/>
+      <x:c r="E86" s="40"/>
+      <x:c r="F86" s="40" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="G86" s="40" t="str">
+        <x:v>stop_sale / maintenance。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" ht="36" customHeight="1">
+      <x:c r="A87" s="40" t="str">
+        <x:v>room_inventory_blocks</x:v>
+      </x:c>
+      <x:c r="B87" s="40" t="str">
+        <x:v>start_date / end_date</x:v>
+      </x:c>
+      <x:c r="C87" s="40" t="str">
+        <x:v>DATE</x:v>
+      </x:c>
+      <x:c r="D87" s="40"/>
+      <x:c r="E87" s="40"/>
+      <x:c r="F87" s="40" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="G87" s="40" t="str">
+        <x:v>DB上の半開区間 [start,end)。APIではendDateExclusive。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" ht="36" customHeight="1">
+      <x:c r="A88" s="40" t="str">
+        <x:v>room_inventory_blocks</x:v>
+      </x:c>
+      <x:c r="B88" s="40" t="str">
+        <x:v>record_status / version</x:v>
+      </x:c>
+      <x:c r="C88" s="40" t="str">
+        <x:v>VARCHAR / INTEGER</x:v>
+      </x:c>
+      <x:c r="D88" s="40"/>
+      <x:c r="E88" s="40"/>
+      <x:c r="F88" s="40" t="str">
+        <x:v>NO</x:v>
+      </x:c>
+      <x:c r="G88" s="40" t="str">
+        <x:v>有効状態と楽観ロック版。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" ht="36" customHeight="1">
+      <x:c r="A89" s="40" t="str">
+        <x:v>room_inventory_block_events</x:v>
+      </x:c>
+      <x:c r="B89" s="40" t="str">
+        <x:v>before_* / after_*</x:v>
+      </x:c>
+      <x:c r="C89" s="40" t="str">
+        <x:v>VARCHAR / DATE</x:v>
+      </x:c>
+      <x:c r="D89" s="40"/>
+      <x:c r="E89" s="40"/>
+      <x:c r="F89" s="40" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="G89" s="40" t="str">
+        <x:v>種別・期間・理由・状態の変更前後を列別に追記監査。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" ht="36" customHeight="1">
+      <x:c r="A90" s="40" t="str">
+        <x:v>reservations</x:v>
+      </x:c>
+      <x:c r="B90" s="40" t="str">
+        <x:v>cancellation_reason / cancelled_by / cancelled_at</x:v>
+      </x:c>
+      <x:c r="C90" s="40" t="str">
+        <x:v>VARCHAR / VARCHAR / TIMESTAMPTZ</x:v>
+      </x:c>
+      <x:c r="D90" s="40"/>
+      <x:c r="E90" s="40"/>
+      <x:c r="F90" s="40" t="str">
+        <x:v>YES</x:v>
+      </x:c>
+      <x:c r="G90" s="40" t="str">
+        <x:v>取消理由・操作者・時刻。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" ht="36" customHeight="1">
+      <x:c r="A91" s="40" t="str">
+        <x:v>MIG-005</x:v>
+      </x:c>
+      <x:c r="B91" s="40" t="str">
+        <x:v>Flyway</x:v>
+      </x:c>
+      <x:c r="C91" s="40" t="str">
+        <x:v>V5__room_inventory_calendar.sql</x:v>
+      </x:c>
+      <x:c r="D91" s="40" t="str">
+        <x:v>在庫テーブル、監査、GiST排他制約、予約との相互競合trigger</x:v>
+      </x:c>
+      <x:c r="E91" s="40" t="str">
+        <x:v>アプリ起動時</x:v>
+      </x:c>
+      <x:c r="F91" s="40" t="str">
+        <x:v>PostgreSQL</x:v>
+      </x:c>
+      <x:c r="G91" s="40" t="str">
+        <x:v>H2ではService競合テストを実施</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -13408,7 +14198,7 @@
         <x:v>何念童</x:v>
       </x:c>
       <x:c r="C3" s="27" t="str">
-        <x:v>2026-07-13</x:v>
+        <x:v>2026-09-30</x:v>
       </x:c>
       <x:c r="D3" s="27" t="str">
         <x:v>何念童</x:v>
@@ -13957,7 +14747,7 @@
         <x:v>清掃状態更新</x:v>
       </x:c>
       <x:c r="F25" s="30" t="str">
-        <x:v>CleaningRequest</x:v>
+        <x:v>CleaningRequest（同日他予約の宿泊状態を保護）</x:v>
       </x:c>
       <x:c r="G25" s="30" t="str">
         <x:v>MessageResponse</x:v>
@@ -13993,14 +14783,30 @@
       </x:c>
     </x:row>
     <x:row r="27" ht="15" hidden="0" customHeight="1">
-      <x:c r="A27" s="19"/>
-      <x:c r="B27" s="19"/>
-      <x:c r="C27" s="19"/>
-      <x:c r="D27" s="19"/>
-      <x:c r="E27" s="19"/>
-      <x:c r="F27" s="19"/>
-      <x:c r="G27" s="19"/>
-      <x:c r="H27" s="19"/>
+      <x:c r="A27" s="19" t="str">
+        <x:v>API-010A</x:v>
+      </x:c>
+      <x:c r="B27" s="19" t="str">
+        <x:v>Reservation</x:v>
+      </x:c>
+      <x:c r="C27" s="19" t="str">
+        <x:v>GET</x:v>
+      </x:c>
+      <x:c r="D27" s="19" t="str">
+        <x:v>/api/reservations/available-rooms</x:v>
+      </x:c>
+      <x:c r="E27" s="19" t="str">
+        <x:v>宿泊日程・人数に合う予約可能客室を取得</x:v>
+      </x:c>
+      <x:c r="F27" s="19" t="str">
+        <x:v>checkInDate / checkOutDate / guestCount</x:v>
+      </x:c>
+      <x:c r="G27" s="19" t="str">
+        <x:v>List&lt;Room&gt;</x:v>
+      </x:c>
+      <x:c r="H27" s="19" t="str">
+        <x:v>アプリ内認証なし（社内NW/Proxy前提）</x:v>
+      </x:c>
     </x:row>
     <x:row r="28" ht="15" hidden="0" customHeight="1">
       <x:c r="A28" s="26" t="str">
@@ -14718,6 +15524,214 @@
       </x:c>
       <x:c r="H56" s="30"/>
     </x:row>
+    <x:row r="57" ht="36" customHeight="1">
+      <x:c r="A57" s="40" t="str">
+        <x:v>API-CAL-001</x:v>
+      </x:c>
+      <x:c r="B57" s="40" t="str">
+        <x:v>Calendar</x:v>
+      </x:c>
+      <x:c r="C57" s="40" t="str">
+        <x:v>GET</x:v>
+      </x:c>
+      <x:c r="D57" s="40" t="str">
+        <x:v>/api/room-calendar?month=YYYY-MM</x:v>
+      </x:c>
+      <x:c r="E57" s="40" t="str">
+        <x:v>自然月の客室・予約・ブロック取得</x:v>
+      </x:c>
+      <x:c r="F57" s="40" t="str">
+        <x:v>month</x:v>
+      </x:c>
+      <x:c r="G57" s="40" t="str">
+        <x:v>CalendarView</x:v>
+      </x:c>
+      <x:c r="H57" s="40" t="str">
+        <x:v>管理者</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="36" customHeight="1">
+      <x:c r="A58" s="40" t="str">
+        <x:v>API-CAL-002</x:v>
+      </x:c>
+      <x:c r="B58" s="40" t="str">
+        <x:v>Calendar</x:v>
+      </x:c>
+      <x:c r="C58" s="40" t="str">
+        <x:v>GET</x:v>
+      </x:c>
+      <x:c r="D58" s="40" t="str">
+        <x:v>/api/room-calendar/reservations/{id}</x:v>
+      </x:c>
+      <x:c r="E58" s="40" t="str">
+        <x:v>予約詳細と許可操作取得</x:v>
+      </x:c>
+      <x:c r="F58" s="40" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G58" s="40" t="str">
+        <x:v>ReservationDetail</x:v>
+      </x:c>
+      <x:c r="H58" s="40" t="str">
+        <x:v>管理者</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="36" customHeight="1">
+      <x:c r="A59" s="40" t="str">
+        <x:v>API-CAL-003</x:v>
+      </x:c>
+      <x:c r="B59" s="40" t="str">
+        <x:v>Inventory</x:v>
+      </x:c>
+      <x:c r="C59" s="40" t="str">
+        <x:v>POST</x:v>
+      </x:c>
+      <x:c r="D59" s="40" t="str">
+        <x:v>/api/room-calendar/blocks</x:v>
+      </x:c>
+      <x:c r="E59" s="40" t="str">
+        <x:v>在庫ブロック作成</x:v>
+      </x:c>
+      <x:c r="F59" s="40" t="str">
+        <x:v>blockType / roomId / [start,end)</x:v>
+      </x:c>
+      <x:c r="G59" s="40" t="str">
+        <x:v>BlockView</x:v>
+      </x:c>
+      <x:c r="H59" s="40" t="str">
+        <x:v>管理者</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="36" customHeight="1">
+      <x:c r="A60" s="40" t="str">
+        <x:v>API-CAL-004</x:v>
+      </x:c>
+      <x:c r="B60" s="40" t="str">
+        <x:v>Inventory</x:v>
+      </x:c>
+      <x:c r="C60" s="40" t="str">
+        <x:v>PUT</x:v>
+      </x:c>
+      <x:c r="D60" s="40" t="str">
+        <x:v>/api/room-calendar/blocks/{id}</x:v>
+      </x:c>
+      <x:c r="E60" s="40" t="str">
+        <x:v>在庫ブロック更新</x:v>
+      </x:c>
+      <x:c r="F60" s="40" t="str">
+        <x:v>version / period / reason</x:v>
+      </x:c>
+      <x:c r="G60" s="40" t="str">
+        <x:v>BlockView</x:v>
+      </x:c>
+      <x:c r="H60" s="40" t="str">
+        <x:v>管理者</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="36" customHeight="1">
+      <x:c r="A61" s="40" t="str">
+        <x:v>API-CAL-005</x:v>
+      </x:c>
+      <x:c r="B61" s="40" t="str">
+        <x:v>Inventory</x:v>
+      </x:c>
+      <x:c r="C61" s="40" t="str">
+        <x:v>POST</x:v>
+      </x:c>
+      <x:c r="D61" s="40" t="str">
+        <x:v>/api/room-calendar/blocks/{id}/release</x:v>
+      </x:c>
+      <x:c r="E61" s="40" t="str">
+        <x:v>全部／一部解除</x:v>
+      </x:c>
+      <x:c r="F61" s="40" t="str">
+        <x:v>[releaseStart,releaseEnd)</x:v>
+      </x:c>
+      <x:c r="G61" s="40" t="str">
+        <x:v>ReleaseResult</x:v>
+      </x:c>
+      <x:c r="H61" s="40" t="str">
+        <x:v>管理者</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="36" customHeight="1">
+      <x:c r="A62" s="40" t="str">
+        <x:v>API-CAL-006</x:v>
+      </x:c>
+      <x:c r="B62" s="40" t="str">
+        <x:v>Booking</x:v>
+      </x:c>
+      <x:c r="C62" s="40" t="str">
+        <x:v>POST</x:v>
+      </x:c>
+      <x:c r="D62" s="40" t="str">
+        <x:v>/api/booking-requests/{id}/cancel</x:v>
+      </x:c>
+      <x:c r="E62" s="40" t="str">
+        <x:v>公開予約をグループ単位で取消</x:v>
+      </x:c>
+      <x:c r="F62" s="40" t="str">
+        <x:v>reason</x:v>
+      </x:c>
+      <x:c r="G62" s="40" t="str">
+        <x:v>MessageResponse</x:v>
+      </x:c>
+      <x:c r="H62" s="40" t="str">
+        <x:v>管理者</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="36" customHeight="1">
+      <x:c r="A63" s="40" t="str">
+        <x:v>API-CAL-007</x:v>
+      </x:c>
+      <x:c r="B63" s="40" t="str">
+        <x:v>Room</x:v>
+      </x:c>
+      <x:c r="C63" s="40" t="str">
+        <x:v>POST</x:v>
+      </x:c>
+      <x:c r="D63" s="40" t="str">
+        <x:v>/api/rooms/{id}/cleaning-status</x:v>
+      </x:c>
+      <x:c r="E63" s="40" t="str">
+        <x:v>清掃状態更新</x:v>
+      </x:c>
+      <x:c r="F63" s="40" t="str">
+        <x:v>cleaningStatus</x:v>
+      </x:c>
+      <x:c r="G63" s="40" t="str">
+        <x:v>MessageResponse</x:v>
+      </x:c>
+      <x:c r="H63" s="40" t="str">
+        <x:v>管理者</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" ht="36" customHeight="1">
+      <x:c r="A64" s="40" t="str">
+        <x:v>API-CAL-008</x:v>
+      </x:c>
+      <x:c r="B64" s="40" t="str">
+        <x:v>Reservation</x:v>
+      </x:c>
+      <x:c r="C64" s="40" t="str">
+        <x:v>POST</x:v>
+      </x:c>
+      <x:c r="D64" s="40" t="str">
+        <x:v>/api/reservations/{id}/cancel</x:v>
+      </x:c>
+      <x:c r="E64" s="40" t="str">
+        <x:v>直接予約取消と理由保存</x:v>
+      </x:c>
+      <x:c r="F64" s="40" t="str">
+        <x:v>reason（任意）</x:v>
+      </x:c>
+      <x:c r="G64" s="40" t="str">
+        <x:v>MessageResponse</x:v>
+      </x:c>
+      <x:c r="H64" s="40" t="str">
+        <x:v>管理者</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:H1"/>
